--- a/output/yearly_benthic_cover_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_27_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.34304861269726</v>
+        <v>45.58569382511799</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3356359622726</v>
+        <v>98.91745826707685</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99723265892356</v>
+        <v>87.9933645729688</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88701061042733</v>
+        <v>45.88870521604794</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228685054645902</v>
+        <v>2.228673840997331</v>
       </c>
       <c r="E3" t="n">
-        <v>5.681007751988949</v>
+        <v>5.681750537632253</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428950182153009</v>
+        <v>0.7428912803324439</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95895165424874</v>
+        <v>33.9595830544729</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17317083790384</v>
+        <v>34.17299889529242</v>
       </c>
       <c r="I3" t="n">
-        <v>6.56942847807519</v>
+        <v>6.564396462163685</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64309386384563</v>
+        <v>4.643070502077774</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00276734107645</v>
+        <v>12.00663542703119</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8744084340286</v>
+        <v>48.86902518411697</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641863855324</v>
+        <v>106.7643658271961</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0340995069931</v>
+        <v>87.09686685175879</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56082694912333</v>
+        <v>42.62812272308098</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18199205930616</v>
+        <v>2.185530279152307</v>
       </c>
       <c r="E4" t="n">
-        <v>6.476323141737113</v>
+        <v>6.48539543120361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444559166086842</v>
+        <v>0.7444498463911806</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24748048068432</v>
+        <v>33.30217982893577</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24497216399947</v>
+        <v>34.2446929339943</v>
       </c>
       <c r="I4" t="n">
-        <v>5.486026265853089</v>
+        <v>5.481806992136736</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652849478804275</v>
+        <v>4.652811539944878</v>
       </c>
       <c r="K4" t="n">
-        <v>12.9659004930069</v>
+        <v>12.90313314824121</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2907884334788</v>
+        <v>44.28639978250659</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81751587560902</v>
+        <v>99.81765565382878</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.92762098700301</v>
+        <v>85.96809144948602</v>
       </c>
       <c r="C5" t="n">
-        <v>42.30572117082578</v>
+        <v>42.35014206565129</v>
       </c>
       <c r="D5" t="n">
-        <v>2.128153055510068</v>
+        <v>2.130528929682771</v>
       </c>
       <c r="E5" t="n">
-        <v>7.079826547722925</v>
+        <v>7.084896146439696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457785286414239</v>
+        <v>0.7457708053741728</v>
       </c>
       <c r="G5" t="n">
-        <v>32.42712404529967</v>
+        <v>32.46409268443779</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3058123175055</v>
+        <v>34.30545704721195</v>
       </c>
       <c r="I5" t="n">
-        <v>4.57981068831452</v>
+        <v>4.576278302751063</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661115804008898</v>
+        <v>4.66106753358858</v>
       </c>
       <c r="K5" t="n">
-        <v>14.07237901299701</v>
+        <v>14.031908550514</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46951019768132</v>
+        <v>43.46567696738646</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8476103815041</v>
+        <v>99.84772758355174</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.43959061259763</v>
+        <v>84.67475725806031</v>
       </c>
       <c r="C6" t="n">
-        <v>41.52893662059019</v>
+        <v>41.76754858322419</v>
       </c>
       <c r="D6" t="n">
-        <v>2.055189641417071</v>
+        <v>2.067521546059249</v>
       </c>
       <c r="E6" t="n">
-        <v>7.474140328474734</v>
+        <v>7.511920186295617</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469038163755842</v>
+        <v>0.7468920847234332</v>
       </c>
       <c r="G6" t="n">
-        <v>31.31536487298058</v>
+        <v>31.50401300034614</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35757555327687</v>
+        <v>34.35703589727792</v>
       </c>
       <c r="I6" t="n">
-        <v>3.822267547725391</v>
+        <v>3.819299013836499</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6681488523474</v>
+        <v>4.668075529521457</v>
       </c>
       <c r="K6" t="n">
-        <v>15.56040938740236</v>
+        <v>15.32524274193967</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78343702844317</v>
+        <v>42.78008983309308</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87278303643572</v>
+        <v>99.87288115825694</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.8807521879027</v>
+        <v>83.12784863928393</v>
       </c>
       <c r="C7" t="n">
-        <v>40.5636307272927</v>
+        <v>40.81389639501423</v>
       </c>
       <c r="D7" t="n">
-        <v>1.979288857334673</v>
+        <v>1.992216053663626</v>
       </c>
       <c r="E7" t="n">
-        <v>7.729662194161047</v>
+        <v>7.769449010725892</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478618622060331</v>
+        <v>0.7478465213493468</v>
       </c>
       <c r="G7" t="n">
-        <v>30.15884836482676</v>
+        <v>30.3565399711286</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40164566147752</v>
+        <v>34.40093998206994</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189308609108974</v>
+        <v>3.1868163419131</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674136638787706</v>
+        <v>4.674040758433417</v>
       </c>
       <c r="K7" t="n">
-        <v>17.11924781209728</v>
+        <v>16.87215136071606</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2109473620621</v>
+        <v>42.20786060499646</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89382590145209</v>
+        <v>99.89390836072675</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.68065978135402</v>
+        <v>87.97827444177744</v>
       </c>
       <c r="C8" t="n">
-        <v>42.81409445991279</v>
+        <v>43.08382810390533</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983514640413568</v>
+        <v>1.996476058362304</v>
       </c>
       <c r="E8" t="n">
-        <v>9.526913368880596</v>
+        <v>9.581285385667352</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494585477989165</v>
+        <v>0.7494456600014924</v>
       </c>
       <c r="G8" t="n">
-        <v>30.6456160240934</v>
+        <v>30.84874821159008</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47509319875016</v>
+        <v>34.47450036006864</v>
       </c>
       <c r="I8" t="n">
-        <v>5.615948077674157</v>
+        <v>5.64378339107824</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684115923743228</v>
+        <v>4.684035375009326</v>
       </c>
       <c r="K8" t="n">
-        <v>12.31934021864597</v>
+        <v>12.02172555822257</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67976586914522</v>
+        <v>44.70672164118277</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81320054770399</v>
+        <v>99.81227530331067</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.65309006497245</v>
+        <v>85.94282054018518</v>
       </c>
       <c r="C9" t="n">
-        <v>41.65792565337075</v>
+        <v>41.92436021834543</v>
       </c>
       <c r="D9" t="n">
-        <v>1.891559050565956</v>
+        <v>1.904166605317992</v>
       </c>
       <c r="E9" t="n">
-        <v>9.866662348744567</v>
+        <v>9.923574507859833</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508260148140081</v>
+        <v>0.7508152523473527</v>
       </c>
       <c r="G9" t="n">
-        <v>29.22488756546636</v>
+        <v>29.42241952480909</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53799668144438</v>
+        <v>34.53750160797821</v>
       </c>
       <c r="I9" t="n">
-        <v>4.688495811349632</v>
+        <v>4.711747714701744</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692662592587551</v>
+        <v>4.692595327170953</v>
       </c>
       <c r="K9" t="n">
-        <v>14.34690993502756</v>
+        <v>14.0571794598148</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83916585388852</v>
+        <v>43.8616885609765</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84400144228684</v>
+        <v>99.84322823913674</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.42267403475634</v>
+        <v>83.74138247061779</v>
       </c>
       <c r="C10" t="n">
-        <v>40.15469892317336</v>
+        <v>40.45394722558655</v>
       </c>
       <c r="D10" t="n">
-        <v>1.791411765395841</v>
+        <v>1.80536672616059</v>
       </c>
       <c r="E10" t="n">
-        <v>9.996476895720168</v>
+        <v>10.06411220777095</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520000058176548</v>
+        <v>0.7519905606135467</v>
       </c>
       <c r="G10" t="n">
-        <v>27.67759611389491</v>
+        <v>27.89580337396862</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59200026761213</v>
+        <v>34.59156578822314</v>
       </c>
       <c r="I10" t="n">
-        <v>3.913188949955291</v>
+        <v>3.932602810046275</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700000036360343</v>
+        <v>4.699941003834667</v>
       </c>
       <c r="K10" t="n">
-        <v>16.57732596524366</v>
+        <v>16.2586175293822</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13773911682329</v>
+        <v>43.15655336406729</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86976400524031</v>
+        <v>99.86911811903605</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.05489125458935</v>
+        <v>81.56082037217109</v>
       </c>
       <c r="C11" t="n">
-        <v>38.39320046593315</v>
+        <v>38.88290560479566</v>
       </c>
       <c r="D11" t="n">
-        <v>1.686194993836088</v>
+        <v>1.708656449753632</v>
       </c>
       <c r="E11" t="n">
-        <v>9.953572170743072</v>
+        <v>10.07192302704728</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530098392419621</v>
+        <v>0.7529990944022975</v>
       </c>
       <c r="G11" t="n">
-        <v>26.05198029295869</v>
+        <v>26.40147492767672</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63845260513027</v>
+        <v>34.63795834250568</v>
       </c>
       <c r="I11" t="n">
-        <v>3.265369857417002</v>
+        <v>3.281564190771118</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706311495262264</v>
+        <v>4.70624434001436</v>
       </c>
       <c r="K11" t="n">
-        <v>18.94510874541066</v>
+        <v>18.4391796278289</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55299109560188</v>
+        <v>42.5686758004297</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89130030694569</v>
+        <v>99.89076103305428</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.62604170823964</v>
+        <v>79.17075489001263</v>
       </c>
       <c r="C12" t="n">
-        <v>36.46943134173802</v>
+        <v>37.00076082099521</v>
       </c>
       <c r="D12" t="n">
-        <v>1.579358869241514</v>
+        <v>1.603546693875029</v>
       </c>
       <c r="E12" t="n">
-        <v>9.776968254107217</v>
+        <v>9.908636511373993</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538795311276077</v>
+        <v>0.7538670717502935</v>
       </c>
       <c r="G12" t="n">
-        <v>24.40134521060564</v>
+        <v>24.77736108964726</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67845843186997</v>
+        <v>34.6778853005135</v>
       </c>
       <c r="I12" t="n">
-        <v>2.724284341740127</v>
+        <v>2.737789024413219</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71174706954755</v>
+        <v>4.711669198439335</v>
       </c>
       <c r="K12" t="n">
-        <v>21.37395829176037</v>
+        <v>20.82924510998738</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06590564824003</v>
+        <v>42.07883950816264</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90929528173842</v>
+        <v>99.90884543914522</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.20900698480521</v>
+        <v>76.9213712013962</v>
       </c>
       <c r="C13" t="n">
-        <v>34.47288996688926</v>
+        <v>35.1742761536431</v>
       </c>
       <c r="D13" t="n">
-        <v>1.474066062077007</v>
+        <v>1.505640478441233</v>
       </c>
       <c r="E13" t="n">
-        <v>9.503905571210645</v>
+        <v>9.684279164450929</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546288679003946</v>
+        <v>0.7546131335774262</v>
       </c>
       <c r="G13" t="n">
-        <v>22.77455462750735</v>
+        <v>23.26455347263812</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71292792341816</v>
+        <v>34.7122041445616</v>
       </c>
       <c r="I13" t="n">
-        <v>2.272493508314193</v>
+        <v>2.283748722867975</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716430424377467</v>
+        <v>4.716332084858914</v>
       </c>
       <c r="K13" t="n">
-        <v>23.79099301519478</v>
+        <v>23.07862879860381</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66044245286763</v>
+        <v>41.67104535263051</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92432543495167</v>
+        <v>99.92395030487742</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.1897304097227</v>
+        <v>83.66764519215005</v>
       </c>
       <c r="C14" t="n">
-        <v>38.86868586065566</v>
+        <v>39.25980221694604</v>
       </c>
       <c r="D14" t="n">
-        <v>1.475753454392651</v>
+        <v>1.507507976549887</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93611889672981</v>
+        <v>11.98360072334949</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554927063575831</v>
+        <v>0.7555491064208109</v>
       </c>
       <c r="G14" t="n">
-        <v>24.74581454977748</v>
+        <v>25.06183970504447</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69785393561403</v>
+        <v>36.5236892951589</v>
       </c>
       <c r="I14" t="n">
-        <v>2.856867452116254</v>
+        <v>3.113276470496429</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721829414734895</v>
+        <v>4.722181915130068</v>
       </c>
       <c r="K14" t="n">
-        <v>16.81026959027729</v>
+        <v>16.33235480784994</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22592451975859</v>
+        <v>44.30419565022634</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90487997069154</v>
+        <v>99.89635267502231</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.4034584908685</v>
+        <v>83.01117995475137</v>
       </c>
       <c r="C15" t="n">
-        <v>38.52369483453054</v>
+        <v>39.08443178375711</v>
       </c>
       <c r="D15" t="n">
-        <v>1.446737545832457</v>
+        <v>1.483384061597151</v>
       </c>
       <c r="E15" t="n">
-        <v>12.09860343968926</v>
+        <v>12.22468345266659</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562209737568255</v>
+        <v>0.7563370479220322</v>
       </c>
       <c r="G15" t="n">
-        <v>24.25926831125325</v>
+        <v>24.66078730664373</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73322932761791</v>
+        <v>36.56177885191808</v>
       </c>
       <c r="I15" t="n">
-        <v>2.383017806738629</v>
+        <v>2.597102684491084</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72638108598016</v>
+        <v>4.727106549512701</v>
       </c>
       <c r="K15" t="n">
-        <v>17.59654150913151</v>
+        <v>16.98882004524865</v>
       </c>
       <c r="L15" t="n">
-        <v>43.80040622711248</v>
+        <v>43.84026826903599</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92064257077453</v>
+        <v>99.91352009804174</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.92190463632087</v>
+        <v>80.67600468290692</v>
       </c>
       <c r="C16" t="n">
-        <v>36.41025111136454</v>
+        <v>37.15072530316439</v>
       </c>
       <c r="D16" t="n">
-        <v>1.352891950323372</v>
+        <v>1.39435034934737</v>
       </c>
       <c r="E16" t="n">
-        <v>11.64505178642149</v>
+        <v>11.8519812497845</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568478293877587</v>
+        <v>0.7570139816272785</v>
       </c>
       <c r="G16" t="n">
-        <v>22.68564116108881</v>
+        <v>23.18063021330894</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76367867039662</v>
+        <v>36.59450222636685</v>
       </c>
       <c r="I16" t="n">
-        <v>1.987494305029329</v>
+        <v>2.166189277301497</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730298933673493</v>
+        <v>4.731337385170491</v>
       </c>
       <c r="K16" t="n">
-        <v>20.07809536367913</v>
+        <v>19.32399531709308</v>
       </c>
       <c r="L16" t="n">
-        <v>43.44545858588025</v>
+        <v>43.45313763850669</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93380506092393</v>
+        <v>99.92785825876416</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.6248245691533</v>
+        <v>82.34196181467446</v>
       </c>
       <c r="C17" t="n">
-        <v>37.65581716945108</v>
+        <v>38.35253621643694</v>
       </c>
       <c r="D17" t="n">
-        <v>1.353978795239279</v>
+        <v>1.395586892200474</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4265203733881</v>
+        <v>12.62984722751355</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574558426258361</v>
+        <v>0.7576853195224633</v>
       </c>
       <c r="G17" t="n">
-        <v>23.14811293575267</v>
+        <v>23.60342871299482</v>
       </c>
       <c r="H17" t="n">
-        <v>37.23746002783187</v>
+        <v>37.02919646486612</v>
       </c>
       <c r="I17" t="n">
-        <v>1.967197577904076</v>
+        <v>2.190683950561651</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734099016411476</v>
+        <v>4.735533247015396</v>
       </c>
       <c r="K17" t="n">
-        <v>18.3751754308467</v>
+        <v>17.65803818532553</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9034867830525</v>
+        <v>43.91646750085101</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93447938335026</v>
+        <v>99.92704190261348</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.15828163700363</v>
+        <v>80.13365779864986</v>
       </c>
       <c r="C18" t="n">
-        <v>35.49274690067621</v>
+        <v>36.48250579600693</v>
       </c>
       <c r="D18" t="n">
-        <v>1.264416433508895</v>
+        <v>1.314683216501608</v>
       </c>
       <c r="E18" t="n">
-        <v>11.87794728992509</v>
+        <v>12.20217426402685</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579790891437371</v>
+        <v>0.7582611319760935</v>
       </c>
       <c r="G18" t="n">
-        <v>21.61692229124831</v>
+        <v>22.23511252096861</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26318346964664</v>
+        <v>37.0573372667571</v>
       </c>
       <c r="I18" t="n">
-        <v>1.640463756382584</v>
+        <v>1.826957323568999</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737369307148358</v>
+        <v>4.739132074850585</v>
       </c>
       <c r="K18" t="n">
-        <v>20.84171836299639</v>
+        <v>19.86634220135014</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61089035916341</v>
+        <v>43.59029967068289</v>
       </c>
       <c r="M18" t="n">
-        <v>99.945355622836</v>
+        <v>99.93914766803996</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.15349231413812</v>
+        <v>79.31192515271823</v>
       </c>
       <c r="C19" t="n">
-        <v>34.7294377504147</v>
+        <v>35.94224256025946</v>
       </c>
       <c r="D19" t="n">
-        <v>1.228127824478447</v>
+        <v>1.285288602393551</v>
       </c>
       <c r="E19" t="n">
-        <v>11.76678358483029</v>
+        <v>12.18325598848135</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584247047627324</v>
+        <v>0.758746626329572</v>
       </c>
       <c r="G19" t="n">
-        <v>20.99651905962332</v>
+        <v>21.73796420113053</v>
       </c>
       <c r="H19" t="n">
-        <v>37.28509048107399</v>
+        <v>37.08106409019467</v>
       </c>
       <c r="I19" t="n">
-        <v>1.378392254602268</v>
+        <v>1.52343922962873</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740154404767078</v>
+        <v>4.742166414559827</v>
       </c>
       <c r="K19" t="n">
-        <v>21.84650768586187</v>
+        <v>20.68807484728176</v>
       </c>
       <c r="L19" t="n">
-        <v>43.37813515124186</v>
+        <v>43.31893377791519</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95408058751843</v>
+        <v>99.9492511854564</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.58487707317789</v>
+        <v>76.8298804243185</v>
       </c>
       <c r="C20" t="n">
-        <v>32.37268330142933</v>
+        <v>33.69479947182814</v>
       </c>
       <c r="D20" t="n">
-        <v>1.135897844217541</v>
+        <v>1.195334660313459</v>
       </c>
       <c r="E20" t="n">
-        <v>11.07466171405967</v>
+        <v>11.54228758755447</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588090910956093</v>
+        <v>0.7591647728857395</v>
       </c>
       <c r="G20" t="n">
-        <v>19.41972184045831</v>
+        <v>20.216581712368</v>
       </c>
       <c r="H20" t="n">
-        <v>37.30398738555376</v>
+        <v>37.10149952767838</v>
       </c>
       <c r="I20" t="n">
-        <v>1.149242378445452</v>
+        <v>1.270232332982571</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742556819347559</v>
+        <v>4.744779830535873</v>
       </c>
       <c r="K20" t="n">
-        <v>24.4151229268221</v>
+        <v>23.1701195756815</v>
       </c>
       <c r="L20" t="n">
-        <v>43.17390509800962</v>
+        <v>43.09276319611177</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96171132626104</v>
+        <v>99.95768224362141</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.6168527777948</v>
+        <v>82.31534663441234</v>
       </c>
       <c r="C21" t="n">
-        <v>36.18822457731331</v>
+        <v>37.0082337513271</v>
       </c>
       <c r="D21" t="n">
-        <v>1.136622265370685</v>
+        <v>1.196259344704412</v>
       </c>
       <c r="E21" t="n">
-        <v>13.11263138183189</v>
+        <v>13.35911668946006</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592930231319149</v>
+        <v>0.7597520459222838</v>
       </c>
       <c r="G21" t="n">
-        <v>21.20275702057338</v>
+        <v>21.72173442034532</v>
       </c>
       <c r="H21" t="n">
-        <v>39.09842829227995</v>
+        <v>38.61971403371504</v>
       </c>
       <c r="I21" t="n">
-        <v>1.561539400032512</v>
+        <v>1.910319813250938</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745581394574469</v>
+        <v>4.748450287014276</v>
       </c>
       <c r="K21" t="n">
-        <v>18.38314722220519</v>
+        <v>17.68465336558766</v>
       </c>
       <c r="L21" t="n">
-        <v>45.37661006182049</v>
+        <v>45.2434847772688</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94798186133897</v>
+        <v>99.93637189418357</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_27_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.58569382511799</v>
+        <v>45.83520727405773</v>
       </c>
       <c r="M2" t="n">
-        <v>98.91745826707685</v>
+        <v>99.64906479392837</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9933645729688</v>
+        <v>88.05065936898865</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88870521604794</v>
+        <v>45.93880148338024</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228673840997331</v>
+        <v>2.228782828410621</v>
       </c>
       <c r="E3" t="n">
-        <v>5.681750537632253</v>
+        <v>5.713402713068509</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428912803324439</v>
+        <v>0.742927609470207</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9595830544729</v>
+        <v>33.97639180901826</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17299889529242</v>
+        <v>34.17467003562952</v>
       </c>
       <c r="I3" t="n">
-        <v>6.564396462163685</v>
+        <v>6.571186814202752</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643070502077774</v>
+        <v>4.643297559188793</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00663542703119</v>
+        <v>11.94934063101134</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86902518411697</v>
+        <v>48.87599150220169</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643658271961</v>
+        <v>106.7641336165933</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09686685175879</v>
+        <v>87.1658310422616</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62812272308098</v>
+        <v>42.6893414685465</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185530279152307</v>
+        <v>2.186315433892632</v>
       </c>
       <c r="E4" t="n">
-        <v>6.48539543120361</v>
+        <v>6.519119157835717</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444498463911806</v>
+        <v>0.7444866303842107</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30217982893577</v>
+        <v>33.32900310121837</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2446929339943</v>
+        <v>34.24638499767369</v>
       </c>
       <c r="I4" t="n">
-        <v>5.481806992136736</v>
+        <v>5.487480281355674</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652811539944878</v>
+        <v>4.653041439901317</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90313314824121</v>
+        <v>12.83416895773837</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28639978250659</v>
+        <v>44.29395660665394</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81765565382878</v>
+        <v>99.81746703293882</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.96809144948602</v>
+        <v>85.94533580098569</v>
       </c>
       <c r="C5" t="n">
-        <v>42.35014206565129</v>
+        <v>42.32057912113216</v>
       </c>
       <c r="D5" t="n">
-        <v>2.130528929682771</v>
+        <v>2.126606130439919</v>
       </c>
       <c r="E5" t="n">
-        <v>7.084896146439696</v>
+        <v>7.104583112136392</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457708053741728</v>
+        <v>0.7458093749845807</v>
       </c>
       <c r="G5" t="n">
-        <v>32.46409268443779</v>
+        <v>32.41877234078146</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30545704721195</v>
+        <v>34.30723124929072</v>
       </c>
       <c r="I5" t="n">
-        <v>4.576278302751063</v>
+        <v>4.581024999699</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66106753358858</v>
+        <v>4.661308593653629</v>
       </c>
       <c r="K5" t="n">
-        <v>14.031908550514</v>
+        <v>14.05466419901432</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46567696738646</v>
+        <v>43.47232667203807</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84772758355174</v>
+        <v>99.84756999218455</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.67475725806031</v>
+        <v>84.64961322346677</v>
       </c>
       <c r="C6" t="n">
-        <v>41.76754858322419</v>
+        <v>41.73630185300383</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067521546059249</v>
+        <v>2.063549867971128</v>
       </c>
       <c r="E6" t="n">
-        <v>7.511920186295617</v>
+        <v>7.531135604915406</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468920847234332</v>
+        <v>0.7469322110961616</v>
       </c>
       <c r="G6" t="n">
-        <v>31.50401300034614</v>
+        <v>31.45751929614107</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35703589727792</v>
+        <v>34.35888171042344</v>
       </c>
       <c r="I6" t="n">
-        <v>3.819299013836499</v>
+        <v>3.823268213568547</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668075529521457</v>
+        <v>4.66832631935101</v>
       </c>
       <c r="K6" t="n">
-        <v>15.32524274193967</v>
+        <v>15.35038677653325</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78008983309308</v>
+        <v>42.78606067602684</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87288115825694</v>
+        <v>99.87274930556393</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.12784863928393</v>
+        <v>83.14427565497897</v>
       </c>
       <c r="C7" t="n">
-        <v>40.81389639501423</v>
+        <v>40.82480888574271</v>
       </c>
       <c r="D7" t="n">
-        <v>1.992216053663626</v>
+        <v>1.990424255673042</v>
       </c>
       <c r="E7" t="n">
-        <v>7.769449010725892</v>
+        <v>7.795944839199547</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478465213493468</v>
+        <v>0.7478875031992832</v>
       </c>
       <c r="G7" t="n">
-        <v>30.3565399711286</v>
+        <v>30.3427653492588</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40093998206994</v>
+        <v>34.40282514716704</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1868163419131</v>
+        <v>3.190131665485731</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674040758433417</v>
+        <v>4.67429689499552</v>
       </c>
       <c r="K7" t="n">
-        <v>16.87215136071606</v>
+        <v>16.85572434502104</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20786060499646</v>
+        <v>42.2132648744149</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89390836072675</v>
+        <v>99.89379810517866</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.97827444177744</v>
+        <v>88.0531349802398</v>
       </c>
       <c r="C8" t="n">
-        <v>43.08382810390533</v>
+        <v>43.15454080076929</v>
       </c>
       <c r="D8" t="n">
-        <v>1.996476058362304</v>
+        <v>1.994678272107981</v>
       </c>
       <c r="E8" t="n">
-        <v>9.581285385667352</v>
+        <v>9.64784891780786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494456600014924</v>
+        <v>0.7494859190752089</v>
       </c>
       <c r="G8" t="n">
-        <v>30.84874821159008</v>
+        <v>30.85475934806232</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47450036006864</v>
+        <v>34.47635227745962</v>
       </c>
       <c r="I8" t="n">
-        <v>5.64378339107824</v>
+        <v>5.645723251506753</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684035375009326</v>
+        <v>4.684286994220056</v>
       </c>
       <c r="K8" t="n">
-        <v>12.02172555822257</v>
+        <v>11.9468650197602</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70672164118277</v>
+        <v>44.71080475568639</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81227530331067</v>
+        <v>99.81221057621588</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.94282054018518</v>
+        <v>86.10516090053109</v>
       </c>
       <c r="C9" t="n">
-        <v>41.92436021834543</v>
+        <v>42.08292660672059</v>
       </c>
       <c r="D9" t="n">
-        <v>1.904166605317992</v>
+        <v>1.906719745797528</v>
       </c>
       <c r="E9" t="n">
-        <v>9.923574507859833</v>
+        <v>10.00797058964616</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508152523473527</v>
+        <v>0.7508534686965608</v>
       </c>
       <c r="G9" t="n">
-        <v>29.42241952480909</v>
+        <v>29.49416942242427</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53750160797821</v>
+        <v>34.53925956004181</v>
       </c>
       <c r="I9" t="n">
-        <v>4.711747714701744</v>
+        <v>4.71335393457126</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692595327170953</v>
+        <v>4.692834179353505</v>
       </c>
       <c r="K9" t="n">
-        <v>14.0571794598148</v>
+        <v>13.89483909946892</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8616885609765</v>
+        <v>43.8654086479353</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84322823913674</v>
+        <v>99.84317435412481</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.74138247061779</v>
+        <v>83.9814476506329</v>
       </c>
       <c r="C10" t="n">
-        <v>40.45394722558655</v>
+        <v>40.69063246757901</v>
       </c>
       <c r="D10" t="n">
-        <v>1.80536672616059</v>
+        <v>1.811755380671237</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06411220777095</v>
+        <v>10.1651772786728</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519905606135467</v>
+        <v>0.7520258718486642</v>
       </c>
       <c r="G10" t="n">
-        <v>27.89580337396862</v>
+        <v>28.02520940336482</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59156578822314</v>
+        <v>34.59319010503857</v>
       </c>
       <c r="I10" t="n">
-        <v>3.932602810046275</v>
+        <v>3.933927911982666</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699941003834667</v>
+        <v>4.700161699054151</v>
       </c>
       <c r="K10" t="n">
-        <v>16.2586175293822</v>
+        <v>16.01855234936711</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15655336406729</v>
+        <v>43.15988868487136</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86911811903605</v>
+        <v>99.86907350181747</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.56082037217109</v>
+        <v>81.70937201169441</v>
       </c>
       <c r="C11" t="n">
-        <v>38.88290560479566</v>
+        <v>39.02847117228328</v>
       </c>
       <c r="D11" t="n">
-        <v>1.708656449753632</v>
+        <v>1.711138187057961</v>
       </c>
       <c r="E11" t="n">
-        <v>10.07192302704728</v>
+        <v>10.1477571028031</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529990944022975</v>
+        <v>0.7530329565704592</v>
       </c>
       <c r="G11" t="n">
-        <v>26.40147492767672</v>
+        <v>26.4688083844004</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63795834250568</v>
+        <v>34.63951600224113</v>
       </c>
       <c r="I11" t="n">
-        <v>3.281564190771118</v>
+        <v>3.282663400055981</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70624434001436</v>
+        <v>4.706455978565369</v>
       </c>
       <c r="K11" t="n">
-        <v>18.4391796278289</v>
+        <v>18.29062798830561</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5686758004297</v>
+        <v>42.57162506407827</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89076103305428</v>
+        <v>99.89072422466714</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.17075489001263</v>
+        <v>79.32471985722913</v>
       </c>
       <c r="C12" t="n">
-        <v>37.00076082099521</v>
+        <v>37.15200994859666</v>
       </c>
       <c r="D12" t="n">
-        <v>1.603546693875029</v>
+        <v>1.606522249224116</v>
       </c>
       <c r="E12" t="n">
-        <v>9.908636511373993</v>
+        <v>9.983791496118945</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538670717502935</v>
+        <v>0.7538995767644389</v>
       </c>
       <c r="G12" t="n">
-        <v>24.77736108964726</v>
+        <v>24.85055263309878</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6778853005135</v>
+        <v>34.67938053116419</v>
       </c>
       <c r="I12" t="n">
-        <v>2.737789024413219</v>
+        <v>2.738701016080914</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711669198439335</v>
+        <v>4.711872354777742</v>
       </c>
       <c r="K12" t="n">
-        <v>20.82924510998738</v>
+        <v>20.67528014277087</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07883950816264</v>
+        <v>42.08152481418648</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90884543914522</v>
+        <v>99.90881490555401</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.9213712013962</v>
+        <v>76.87619909677181</v>
       </c>
       <c r="C13" t="n">
-        <v>35.1742761536431</v>
+        <v>35.12662033587129</v>
       </c>
       <c r="D13" t="n">
-        <v>1.505640478441233</v>
+        <v>1.500061849357694</v>
       </c>
       <c r="E13" t="n">
-        <v>9.684279164450929</v>
+        <v>9.702941357810293</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546131335774262</v>
+        <v>0.7546463585213223</v>
       </c>
       <c r="G13" t="n">
-        <v>23.26455347263812</v>
+        <v>23.20376574826167</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7122041445616</v>
+        <v>34.71373249198083</v>
       </c>
       <c r="I13" t="n">
-        <v>2.283748722867975</v>
+        <v>2.284511550081731</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716332084858914</v>
+        <v>4.716539740758264</v>
       </c>
       <c r="K13" t="n">
-        <v>23.07862879860381</v>
+        <v>23.1238009032282</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67104535263051</v>
+        <v>41.67350373267602</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92395030487742</v>
+        <v>99.92392497177552</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.66764519215005</v>
+        <v>83.6357482092391</v>
       </c>
       <c r="C14" t="n">
-        <v>39.25980221694604</v>
+        <v>39.36865161368288</v>
       </c>
       <c r="D14" t="n">
-        <v>1.507507976549887</v>
+        <v>1.501783888558531</v>
       </c>
       <c r="E14" t="n">
-        <v>11.98360072334949</v>
+        <v>12.06014335222322</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555491064208109</v>
+        <v>0.755512676541942</v>
       </c>
       <c r="G14" t="n">
-        <v>25.06183970504447</v>
+        <v>25.09640607377229</v>
       </c>
       <c r="H14" t="n">
-        <v>36.5236892951589</v>
+        <v>36.61958601529493</v>
       </c>
       <c r="I14" t="n">
-        <v>3.113276470496429</v>
+        <v>2.88036197446105</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722181915130068</v>
+        <v>4.721954228387137</v>
       </c>
       <c r="K14" t="n">
-        <v>16.33235480784994</v>
+        <v>16.36425179076092</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30419565022634</v>
+        <v>44.17119462317196</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89635267502231</v>
+        <v>99.90409802761576</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.01117995475137</v>
+        <v>82.87248845657238</v>
       </c>
       <c r="C15" t="n">
-        <v>39.08443178375711</v>
+        <v>39.05063651265999</v>
       </c>
       <c r="D15" t="n">
-        <v>1.483384061597151</v>
+        <v>1.473555729509584</v>
       </c>
       <c r="E15" t="n">
-        <v>12.22468345266659</v>
+        <v>12.23389272585719</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563370479220322</v>
+        <v>0.7562427985512596</v>
       </c>
       <c r="G15" t="n">
-        <v>24.66078730664373</v>
+        <v>24.62468351262045</v>
       </c>
       <c r="H15" t="n">
-        <v>36.56177885191808</v>
+        <v>36.65497491948148</v>
       </c>
       <c r="I15" t="n">
-        <v>2.597102684491084</v>
+        <v>2.402621279607049</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727106549512701</v>
+        <v>4.726517490945373</v>
       </c>
       <c r="K15" t="n">
-        <v>16.98882004524865</v>
+        <v>17.1275115434276</v>
       </c>
       <c r="L15" t="n">
-        <v>43.84026826903599</v>
+        <v>43.74184188906628</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91352009804174</v>
+        <v>99.91998994515387</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.67600468290692</v>
+        <v>80.39156292055549</v>
       </c>
       <c r="C16" t="n">
-        <v>37.15072530316439</v>
+        <v>36.941146630467</v>
       </c>
       <c r="D16" t="n">
-        <v>1.39435034934737</v>
+        <v>1.379329605561203</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8519812497845</v>
+        <v>11.78557441204566</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570139816272785</v>
+        <v>0.7568711379482103</v>
       </c>
       <c r="G16" t="n">
-        <v>23.18063021330894</v>
+        <v>23.05006476262444</v>
       </c>
       <c r="H16" t="n">
-        <v>36.59450222636685</v>
+        <v>36.68543043572609</v>
       </c>
       <c r="I16" t="n">
-        <v>2.166189277301497</v>
+        <v>2.003847954473571</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731337385170491</v>
+        <v>4.730444612176314</v>
       </c>
       <c r="K16" t="n">
-        <v>19.32399531709308</v>
+        <v>19.6084370794445</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45313763850669</v>
+        <v>43.3836768100994</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92785825876416</v>
+        <v>99.9332605200109</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.34196181467446</v>
+        <v>82.10106056300637</v>
       </c>
       <c r="C17" t="n">
-        <v>38.35253621643694</v>
+        <v>38.18754911307839</v>
       </c>
       <c r="D17" t="n">
-        <v>1.395586892200474</v>
+        <v>1.380444508317766</v>
       </c>
       <c r="E17" t="n">
-        <v>12.62984722751355</v>
+        <v>12.56935085880055</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576853195224633</v>
+        <v>0.757482911750976</v>
       </c>
       <c r="G17" t="n">
-        <v>23.60342871299482</v>
+        <v>23.5111375709201</v>
       </c>
       <c r="H17" t="n">
-        <v>37.02919646486612</v>
+        <v>37.15752461753132</v>
       </c>
       <c r="I17" t="n">
-        <v>2.190683950561651</v>
+        <v>1.990851897242061</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735533247015396</v>
+        <v>4.7342681984436</v>
       </c>
       <c r="K17" t="n">
-        <v>17.65803818532553</v>
+        <v>17.89893943699362</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91646750085101</v>
+        <v>43.84720331643409</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92704190261348</v>
+        <v>99.93369186650609</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.13365779864986</v>
+        <v>79.74489552524518</v>
       </c>
       <c r="C18" t="n">
-        <v>36.48250579600693</v>
+        <v>36.13875801997847</v>
       </c>
       <c r="D18" t="n">
-        <v>1.314683216501608</v>
+        <v>1.294516973300991</v>
       </c>
       <c r="E18" t="n">
-        <v>12.20217426402685</v>
+        <v>12.06365462228541</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582611319760935</v>
+        <v>0.7580085750760484</v>
       </c>
       <c r="G18" t="n">
-        <v>22.23511252096861</v>
+        <v>22.04765672490525</v>
       </c>
       <c r="H18" t="n">
-        <v>37.0573372667571</v>
+        <v>37.18331047703904</v>
       </c>
       <c r="I18" t="n">
-        <v>1.826957323568999</v>
+        <v>1.66019455841315</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739132074850585</v>
+        <v>4.737553594225302</v>
       </c>
       <c r="K18" t="n">
-        <v>19.86634220135014</v>
+        <v>20.25510447475483</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59029967068289</v>
+        <v>43.55083606367663</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93914766803996</v>
+        <v>99.94469855840993</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.31192515271823</v>
+        <v>78.77253332905097</v>
       </c>
       <c r="C19" t="n">
-        <v>35.94224256025946</v>
+        <v>35.42205727693086</v>
       </c>
       <c r="D19" t="n">
-        <v>1.285288602393551</v>
+        <v>1.259702696489637</v>
       </c>
       <c r="E19" t="n">
-        <v>12.18325598848135</v>
+        <v>11.96993665517443</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758746626329572</v>
+        <v>0.7584526028322349</v>
       </c>
       <c r="G19" t="n">
-        <v>21.73796420113053</v>
+        <v>21.45471492491843</v>
       </c>
       <c r="H19" t="n">
-        <v>37.08106409019467</v>
+        <v>37.20509178989167</v>
       </c>
       <c r="I19" t="n">
-        <v>1.52343922962873</v>
+        <v>1.384305892043105</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742166414559827</v>
+        <v>4.740328767701468</v>
       </c>
       <c r="K19" t="n">
-        <v>20.68807484728176</v>
+        <v>21.22746667094904</v>
       </c>
       <c r="L19" t="n">
-        <v>43.31893377791519</v>
+        <v>43.30435953660863</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9492511854564</v>
+        <v>99.95388348448853</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.8298804243185</v>
+        <v>76.17410241031276</v>
       </c>
       <c r="C20" t="n">
-        <v>33.69479947182814</v>
+        <v>33.03664066790473</v>
       </c>
       <c r="D20" t="n">
-        <v>1.195334660313459</v>
+        <v>1.165918721241078</v>
       </c>
       <c r="E20" t="n">
-        <v>11.54228758755447</v>
+        <v>11.27114514506069</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591647728857395</v>
+        <v>0.7588356656120162</v>
       </c>
       <c r="G20" t="n">
-        <v>20.216581712368</v>
+        <v>19.8574265654583</v>
       </c>
       <c r="H20" t="n">
-        <v>37.10149952767838</v>
+        <v>37.22388253018293</v>
       </c>
       <c r="I20" t="n">
-        <v>1.270232332982571</v>
+        <v>1.154170872682645</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744779830535873</v>
+        <v>4.742722910075101</v>
       </c>
       <c r="K20" t="n">
-        <v>23.1701195756815</v>
+        <v>23.82589758968724</v>
       </c>
       <c r="L20" t="n">
-        <v>43.09276319611177</v>
+        <v>43.09900880096239</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95768224362141</v>
+        <v>99.96154705855437</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.31534663441234</v>
+        <v>82.00419151702835</v>
       </c>
       <c r="C21" t="n">
-        <v>37.0082337513271</v>
+        <v>36.67295172452064</v>
       </c>
       <c r="D21" t="n">
-        <v>1.196259344704412</v>
+        <v>1.166694891384969</v>
       </c>
       <c r="E21" t="n">
-        <v>13.35911668946006</v>
+        <v>13.22614480464795</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597520459222838</v>
+        <v>0.7593408342631726</v>
       </c>
       <c r="G21" t="n">
-        <v>21.72173442034532</v>
+        <v>21.545184945971</v>
       </c>
       <c r="H21" t="n">
-        <v>38.61971403371504</v>
+        <v>38.92320202930487</v>
       </c>
       <c r="I21" t="n">
-        <v>1.910319813250938</v>
+        <v>1.637743797311561</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748450287014276</v>
+        <v>4.745880214144829</v>
       </c>
       <c r="K21" t="n">
-        <v>17.68465336558766</v>
+        <v>17.99580848297165</v>
       </c>
       <c r="L21" t="n">
-        <v>45.2434847772688</v>
+        <v>45.2766846507998</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93637189418357</v>
+        <v>99.94544485829209</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_27_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.83520727405773</v>
+        <v>43.77138603720491</v>
       </c>
       <c r="M2" t="n">
-        <v>99.64906479392837</v>
+        <v>96.31751587155938</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05065936898865</v>
+        <v>81.4185256102854</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93880148338024</v>
+        <v>43.17408116584097</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228782828410621</v>
+        <v>2.176079186870225</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713402713068509</v>
+        <v>4.160528950017221</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742927609470207</v>
+        <v>0.7375917510169812</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97639180901826</v>
+        <v>32.73185776917296</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17467003562952</v>
+        <v>33.92922054678113</v>
       </c>
       <c r="I3" t="n">
-        <v>6.571186814202752</v>
+        <v>3.073298962570755</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643297559188793</v>
+        <v>4.609948443856132</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94934063101134</v>
+        <v>18.58147438971458</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87599150220169</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641336165933</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.1658310422616</v>
+        <v>88.50380966347738</v>
       </c>
       <c r="C4" t="n">
-        <v>42.6893414685465</v>
+        <v>42.79280833040593</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186315433892632</v>
+        <v>2.181782377639587</v>
       </c>
       <c r="E4" t="n">
-        <v>6.519119157835717</v>
+        <v>6.554411716749974</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444866303842107</v>
+        <v>0.739524872978415</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32900310121837</v>
+        <v>33.42924316283422</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24638499767369</v>
+        <v>34.01814415700709</v>
       </c>
       <c r="I4" t="n">
-        <v>5.487480281355674</v>
+        <v>6.958672920152999</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653041439901317</v>
+        <v>4.622030456115094</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83416895773837</v>
+        <v>11.49619033652265</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29395660665394</v>
+        <v>45.47965190267031</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81746703293882</v>
+        <v>99.76865056959888</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.94533580098569</v>
+        <v>87.27932647472946</v>
       </c>
       <c r="C5" t="n">
-        <v>42.32057912113216</v>
+        <v>42.64696129147552</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126606130439919</v>
+        <v>2.123125535262256</v>
       </c>
       <c r="E5" t="n">
-        <v>7.104583112136392</v>
+        <v>7.346825047619718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458093749845807</v>
+        <v>0.741166325085249</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41877234078146</v>
+        <v>32.53050373442374</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30723124929072</v>
+        <v>34.09365095392145</v>
       </c>
       <c r="I5" t="n">
-        <v>4.581024999699</v>
+        <v>5.811765346634227</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661308593653629</v>
+        <v>4.632289531782806</v>
       </c>
       <c r="K5" t="n">
-        <v>14.05466419901432</v>
+        <v>12.72067352527057</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47232667203807</v>
+        <v>44.43906871324968</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84756999218455</v>
+        <v>99.80670352999576</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.64961322346677</v>
+        <v>85.79148762053173</v>
       </c>
       <c r="C6" t="n">
-        <v>41.73630185300383</v>
+        <v>42.06097141967022</v>
       </c>
       <c r="D6" t="n">
-        <v>2.063549867971128</v>
+        <v>2.051776114947665</v>
       </c>
       <c r="E6" t="n">
-        <v>7.531135604915406</v>
+        <v>7.90864023148129</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469322110961616</v>
+        <v>0.7425636424404179</v>
       </c>
       <c r="G6" t="n">
-        <v>31.45751929614107</v>
+        <v>31.43728878060045</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35888171042344</v>
+        <v>34.15792755225922</v>
       </c>
       <c r="I6" t="n">
-        <v>3.823268213568547</v>
+        <v>4.852268533550064</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66832631935101</v>
+        <v>4.641022765252612</v>
       </c>
       <c r="K6" t="n">
-        <v>15.35038677653325</v>
+        <v>14.20851237946828</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78606067602684</v>
+        <v>43.56907827456611</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87274930556393</v>
+        <v>99.83856207370462</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.14427565497897</v>
+        <v>84.0711187371991</v>
       </c>
       <c r="C7" t="n">
-        <v>40.82480888574271</v>
+        <v>41.09382607135248</v>
       </c>
       <c r="D7" t="n">
-        <v>1.990424255673042</v>
+        <v>1.969668062841015</v>
       </c>
       <c r="E7" t="n">
-        <v>7.795944839199547</v>
+        <v>8.267160353604593</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478875031992832</v>
+        <v>0.7437560535500323</v>
       </c>
       <c r="G7" t="n">
-        <v>30.3427653492588</v>
+        <v>30.17923020077574</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40282514716704</v>
+        <v>34.21277846330148</v>
       </c>
       <c r="I7" t="n">
-        <v>3.190131665485731</v>
+        <v>4.050050268438519</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67429689499552</v>
+        <v>4.648475334687702</v>
       </c>
       <c r="K7" t="n">
-        <v>16.85572434502104</v>
+        <v>15.92888126280091</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2132648744149</v>
+        <v>42.84250742880356</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89379810517866</v>
+        <v>99.86521476295695</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.0531349802398</v>
+        <v>82.22008650214563</v>
       </c>
       <c r="C8" t="n">
-        <v>43.15454080076929</v>
+        <v>39.87128941744548</v>
       </c>
       <c r="D8" t="n">
-        <v>1.994678272107981</v>
+        <v>1.882033577205528</v>
       </c>
       <c r="E8" t="n">
-        <v>9.64784891780786</v>
+        <v>8.462615507857281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494859190752089</v>
+        <v>0.7447751262027841</v>
       </c>
       <c r="G8" t="n">
-        <v>30.85475934806232</v>
+        <v>28.83649567336242</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47635227745962</v>
+        <v>34.25965580532807</v>
       </c>
       <c r="I8" t="n">
-        <v>5.645723251506753</v>
+        <v>3.379666273422143</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684286994220056</v>
+        <v>4.6548445387674</v>
       </c>
       <c r="K8" t="n">
-        <v>11.9468650197602</v>
+        <v>17.77991349785438</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71080475568639</v>
+        <v>42.23629568835462</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81221057621588</v>
+        <v>99.88749860365448</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.10516090053109</v>
+        <v>80.17776774203415</v>
       </c>
       <c r="C9" t="n">
-        <v>42.08292660672059</v>
+        <v>38.3529992180474</v>
       </c>
       <c r="D9" t="n">
-        <v>1.906719745797528</v>
+        <v>1.786023744045521</v>
       </c>
       <c r="E9" t="n">
-        <v>10.00797058964616</v>
+        <v>8.500853017366072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508534686965608</v>
+        <v>0.7456482007563332</v>
       </c>
       <c r="G9" t="n">
-        <v>29.49416942242427</v>
+        <v>27.36543417262681</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53925956004181</v>
+        <v>34.29981723479133</v>
       </c>
       <c r="I9" t="n">
-        <v>4.71335393457126</v>
+        <v>2.819690117721002</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692834179353505</v>
+        <v>4.660301254727082</v>
       </c>
       <c r="K9" t="n">
-        <v>13.89483909946892</v>
+        <v>19.82223225796585</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8654086479353</v>
+        <v>41.73088890528059</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84317435412481</v>
+        <v>99.90612038129385</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.9814476506329</v>
+        <v>85.25098825460523</v>
       </c>
       <c r="C10" t="n">
-        <v>40.69063246757901</v>
+        <v>41.90825375290879</v>
       </c>
       <c r="D10" t="n">
-        <v>1.811755380671237</v>
+        <v>1.7879572717775</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1651772786728</v>
+        <v>10.49783257384562</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520258718486642</v>
+        <v>0.7464554304918108</v>
       </c>
       <c r="G10" t="n">
-        <v>28.02520940336482</v>
+        <v>28.92137784609828</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59319010503857</v>
+        <v>35.86326798760569</v>
       </c>
       <c r="I10" t="n">
-        <v>3.933927911982666</v>
+        <v>2.768750704212526</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700161699054151</v>
+        <v>4.665346440573817</v>
       </c>
       <c r="K10" t="n">
-        <v>16.01855234936711</v>
+        <v>14.74901174539477</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15988868487136</v>
+        <v>43.2505426173764</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86907350181747</v>
+        <v>99.90780811567996</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.70937201169441</v>
+        <v>84.73433370776831</v>
       </c>
       <c r="C11" t="n">
-        <v>39.02847117228328</v>
+        <v>41.68075675282904</v>
       </c>
       <c r="D11" t="n">
-        <v>1.711138187057961</v>
+        <v>1.755558151547494</v>
       </c>
       <c r="E11" t="n">
-        <v>10.1477571028031</v>
+        <v>10.7629972751112</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530329565704592</v>
+        <v>0.747157449887168</v>
       </c>
       <c r="G11" t="n">
-        <v>26.4688083844004</v>
+        <v>28.45424340308463</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63951600224113</v>
+        <v>35.95393884659721</v>
       </c>
       <c r="I11" t="n">
-        <v>3.282663400055981</v>
+        <v>2.390704519745814</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706455978565369</v>
+        <v>4.6697340617948</v>
       </c>
       <c r="K11" t="n">
-        <v>18.29062798830561</v>
+        <v>15.26566629223169</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57162506407827</v>
+        <v>42.97396168010729</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89072422466714</v>
+        <v>99.92038472516803</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.32471985722913</v>
+        <v>82.60097631148591</v>
       </c>
       <c r="C12" t="n">
-        <v>37.15200994859666</v>
+        <v>39.91864117775724</v>
       </c>
       <c r="D12" t="n">
-        <v>1.606522249224116</v>
+        <v>1.665489360611567</v>
       </c>
       <c r="E12" t="n">
-        <v>9.983791496118945</v>
+        <v>10.5431118960362</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538995767644389</v>
+        <v>0.7477586231419635</v>
       </c>
       <c r="G12" t="n">
-        <v>24.85055263309878</v>
+        <v>26.99440039073365</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67938053116419</v>
+        <v>35.98286788483726</v>
       </c>
       <c r="I12" t="n">
-        <v>2.738701016080914</v>
+        <v>1.993856761488006</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711872354777742</v>
+        <v>4.673491394637271</v>
       </c>
       <c r="K12" t="n">
-        <v>20.67528014277087</v>
+        <v>17.3990236885141</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08152481418648</v>
+        <v>42.61592667484685</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90881490555401</v>
+        <v>99.93359154111818</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.87619909677181</v>
+        <v>83.78244095120763</v>
       </c>
       <c r="C13" t="n">
-        <v>35.12662033587129</v>
+        <v>40.91426898686427</v>
       </c>
       <c r="D13" t="n">
-        <v>1.500061849357694</v>
+        <v>1.666696950635976</v>
       </c>
       <c r="E13" t="n">
-        <v>9.702941357810293</v>
+        <v>11.18472954999777</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546463585213223</v>
+        <v>0.7483007976375367</v>
       </c>
       <c r="G13" t="n">
-        <v>23.20376574826167</v>
+        <v>27.34420724170489</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71373249198083</v>
+        <v>36.33919196968421</v>
       </c>
       <c r="I13" t="n">
-        <v>2.284511550081731</v>
+        <v>1.822434456312652</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716539740758264</v>
+        <v>4.676879985234603</v>
       </c>
       <c r="K13" t="n">
-        <v>23.1238009032282</v>
+        <v>16.21755904879236</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67350373267602</v>
+        <v>42.8074681634066</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92392497177552</v>
+        <v>99.93929619906322</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.6357482092391</v>
+        <v>81.63334613922616</v>
       </c>
       <c r="C14" t="n">
-        <v>39.36865161368288</v>
+        <v>39.04795562470479</v>
       </c>
       <c r="D14" t="n">
-        <v>1.501783888558531</v>
+        <v>1.57856444946983</v>
       </c>
       <c r="E14" t="n">
-        <v>12.06014335222322</v>
+        <v>10.84657034101705</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755512676541942</v>
+        <v>0.7487651283696601</v>
       </c>
       <c r="G14" t="n">
-        <v>25.09640607377229</v>
+        <v>25.89828548868476</v>
       </c>
       <c r="H14" t="n">
-        <v>36.61958601529493</v>
+        <v>36.3617409281583</v>
       </c>
       <c r="I14" t="n">
-        <v>2.88036197446105</v>
+        <v>1.5196377512162</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721954228387137</v>
+        <v>4.679782052310375</v>
       </c>
       <c r="K14" t="n">
-        <v>16.36425179076092</v>
+        <v>18.36665386077384</v>
       </c>
       <c r="L14" t="n">
-        <v>44.17119462317196</v>
+        <v>42.53476733517935</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90409802761576</v>
+        <v>99.94937682065797</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.87248845657238</v>
+        <v>80.65637954629904</v>
       </c>
       <c r="C15" t="n">
-        <v>39.05063651265999</v>
+        <v>38.27063780840691</v>
       </c>
       <c r="D15" t="n">
-        <v>1.473555729509584</v>
+        <v>1.537444266081802</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23389272585719</v>
+        <v>10.78095304349311</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562427985512596</v>
+        <v>0.7491678905552503</v>
       </c>
       <c r="G15" t="n">
-        <v>24.62468351262045</v>
+        <v>25.22365845708786</v>
       </c>
       <c r="H15" t="n">
-        <v>36.65497491948148</v>
+        <v>36.38129997770962</v>
       </c>
       <c r="I15" t="n">
-        <v>2.402621279607049</v>
+        <v>1.301556595401086</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726517490945373</v>
+        <v>4.682299315970313</v>
       </c>
       <c r="K15" t="n">
-        <v>17.1275115434276</v>
+        <v>19.34362045370097</v>
       </c>
       <c r="L15" t="n">
-        <v>43.74184188906628</v>
+        <v>42.34237984249138</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91998994515387</v>
+        <v>99.95663810459925</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.39156292055549</v>
+        <v>78.20091072825326</v>
       </c>
       <c r="C16" t="n">
-        <v>36.941146630467</v>
+        <v>36.01652658853349</v>
       </c>
       <c r="D16" t="n">
-        <v>1.379329605561203</v>
+        <v>1.437551086124969</v>
       </c>
       <c r="E16" t="n">
-        <v>11.78557441204566</v>
+        <v>10.26133183940948</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568711379482103</v>
+        <v>0.7495144108961707</v>
       </c>
       <c r="G16" t="n">
-        <v>23.05006476262444</v>
+        <v>23.58478834711959</v>
       </c>
       <c r="H16" t="n">
-        <v>36.68543043572609</v>
+        <v>36.39812779511923</v>
       </c>
       <c r="I16" t="n">
-        <v>2.003847954473571</v>
+        <v>1.085132181482763</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730444612176314</v>
+        <v>4.684465068101066</v>
       </c>
       <c r="K16" t="n">
-        <v>19.6084370794445</v>
+        <v>21.79908927174675</v>
       </c>
       <c r="L16" t="n">
-        <v>43.3836768100994</v>
+        <v>42.14822978984751</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9332605200109</v>
+        <v>99.96384565012775</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.10106056300637</v>
+        <v>83.46036879935244</v>
       </c>
       <c r="C17" t="n">
-        <v>38.18754911307839</v>
+        <v>39.55149655204141</v>
       </c>
       <c r="D17" t="n">
-        <v>1.380444508317766</v>
+        <v>1.438196306207776</v>
       </c>
       <c r="E17" t="n">
-        <v>12.56935085880055</v>
+        <v>12.11953184072327</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757482911750976</v>
+        <v>0.7498508175497715</v>
       </c>
       <c r="G17" t="n">
-        <v>23.5111375709201</v>
+        <v>25.26166959660344</v>
       </c>
       <c r="H17" t="n">
-        <v>37.15752461753132</v>
+        <v>38.08076009165767</v>
       </c>
       <c r="I17" t="n">
-        <v>1.990851897242061</v>
+        <v>1.123792536924436</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7342681984436</v>
+        <v>4.686567609686071</v>
       </c>
       <c r="K17" t="n">
-        <v>17.89893943699362</v>
+        <v>16.53963120064757</v>
       </c>
       <c r="L17" t="n">
-        <v>43.84720331643409</v>
+        <v>43.87142930170242</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93369186650609</v>
+        <v>99.9625570543914</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.74489552524518</v>
+        <v>85.25057592056943</v>
       </c>
       <c r="C18" t="n">
-        <v>36.13875801997847</v>
+        <v>40.30230480178827</v>
       </c>
       <c r="D18" t="n">
-        <v>1.294516973300991</v>
+        <v>1.439384157573313</v>
       </c>
       <c r="E18" t="n">
-        <v>12.06365462228541</v>
+        <v>12.73600140516289</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580085750760484</v>
+        <v>0.7504701428211068</v>
       </c>
       <c r="G18" t="n">
-        <v>22.04765672490525</v>
+        <v>25.40973603180885</v>
       </c>
       <c r="H18" t="n">
-        <v>37.18331047703904</v>
+        <v>38.11221218389314</v>
       </c>
       <c r="I18" t="n">
-        <v>1.66019455841315</v>
+        <v>2.112333606678222</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737553594225302</v>
+        <v>4.690438392631917</v>
       </c>
       <c r="K18" t="n">
-        <v>20.25510447475483</v>
+        <v>14.74942407943055</v>
       </c>
       <c r="L18" t="n">
-        <v>43.55083606367663</v>
+        <v>44.87791810531547</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94469855840993</v>
+        <v>99.92964698653429</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.77253332905097</v>
+        <v>82.60320487877452</v>
       </c>
       <c r="C19" t="n">
-        <v>35.42205727693086</v>
+        <v>37.98160036316545</v>
       </c>
       <c r="D19" t="n">
-        <v>1.259702696489637</v>
+        <v>1.344075866697198</v>
       </c>
       <c r="E19" t="n">
-        <v>11.96993665517443</v>
+        <v>12.1862799850985</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584526028322349</v>
+        <v>0.751003606840718</v>
       </c>
       <c r="G19" t="n">
-        <v>21.45471492491843</v>
+        <v>23.72723973638773</v>
       </c>
       <c r="H19" t="n">
-        <v>37.20509178989167</v>
+        <v>38.13930385982773</v>
       </c>
       <c r="I19" t="n">
-        <v>1.384305892043105</v>
+        <v>1.761529281168172</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740328767701468</v>
+        <v>4.693772542754487</v>
       </c>
       <c r="K19" t="n">
-        <v>21.22746667094904</v>
+        <v>17.39679512122546</v>
       </c>
       <c r="L19" t="n">
-        <v>43.30435953660863</v>
+        <v>44.56292858209024</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95388348448853</v>
+        <v>99.94132406648114</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.17410241031276</v>
+        <v>79.88270345049028</v>
       </c>
       <c r="C20" t="n">
-        <v>33.03664066790473</v>
+        <v>35.53275461134659</v>
       </c>
       <c r="D20" t="n">
-        <v>1.165918721241078</v>
+        <v>1.246696837750919</v>
       </c>
       <c r="E20" t="n">
-        <v>11.27114514506069</v>
+        <v>11.54818415833637</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588356656120162</v>
+        <v>0.7514639087103331</v>
       </c>
       <c r="G20" t="n">
-        <v>19.8574265654583</v>
+        <v>22.00818828821115</v>
       </c>
       <c r="H20" t="n">
-        <v>37.22388253018293</v>
+        <v>38.16268003633685</v>
       </c>
       <c r="I20" t="n">
-        <v>1.154170872682645</v>
+        <v>1.468840791705067</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742722910075101</v>
+        <v>4.696649429439582</v>
       </c>
       <c r="K20" t="n">
-        <v>23.82589758968724</v>
+        <v>20.11729654950971</v>
       </c>
       <c r="L20" t="n">
-        <v>43.09900880096239</v>
+        <v>44.30101747022236</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96154705855437</v>
+        <v>99.95106863107867</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.00419151702835</v>
+        <v>77.1274285185216</v>
       </c>
       <c r="C21" t="n">
-        <v>36.67295172452064</v>
+        <v>33.00326392655469</v>
       </c>
       <c r="D21" t="n">
-        <v>1.166694891384969</v>
+        <v>1.148606483978794</v>
       </c>
       <c r="E21" t="n">
-        <v>13.22614480464795</v>
+        <v>10.84368438824786</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593408342631726</v>
+        <v>0.751861650575573</v>
       </c>
       <c r="G21" t="n">
-        <v>21.545184945971</v>
+        <v>20.2765796808061</v>
       </c>
       <c r="H21" t="n">
-        <v>38.92320202930487</v>
+        <v>38.18287913753687</v>
       </c>
       <c r="I21" t="n">
-        <v>1.637743797311561</v>
+        <v>1.224681861279075</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745880214144829</v>
+        <v>4.699135316097331</v>
       </c>
       <c r="K21" t="n">
-        <v>17.99580848297165</v>
+        <v>22.87257148147838</v>
       </c>
       <c r="L21" t="n">
-        <v>45.2766846507998</v>
+        <v>44.08336345886399</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94544485829209</v>
+        <v>99.95919886689708</v>
       </c>
     </row>
   </sheetData>
